--- a/1_Data/Wozniak_2022_PsychRes/Exp2/Codebook_Wozniak_2022_PsychRes_Exp2_Clean.xlsx
+++ b/1_Data/Wozniak_2022_PsychRes/Exp2/Codebook_Wozniak_2022_PsychRes_Exp2_Clean.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Variable_name</t>
   </si>
@@ -147,6 +147,12 @@
   </si>
   <si>
     <t xml:space="preserve">1;0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task type: shape-label matching (this study has two tasks that share the value self-matching: the standard self-matching task, whose labels are the identity words You/none/friend name, and the pseudo-words task, whose labels are the pseudo-words Nenu/Miru/Waru; tell them apart by the Label column; the Shape column holds the identity slot label in both tasks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">self-matching</t>
   </si>
 </sst>
 </file>
@@ -508,10 +514,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
